--- a/reports/qa/mobile/appium_results.xlsx
+++ b/reports/qa/mobile/appium_results.xlsx
@@ -470,7 +470,7 @@
         <v>Timestamp</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-10-27T05:46:35.243Z</v>
+        <v>2026-10-27T06:11:54.998Z</v>
       </c>
     </row>
   </sheetData>

--- a/reports/qa/mobile/appium_results.xlsx
+++ b/reports/qa/mobile/appium_results.xlsx
@@ -3,9 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Audit &amp; Blocker Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Planned Test Scenarios" sheetId="2" r:id="rId2"/>
-    <sheet name="Environment Checklist" sheetId="3" r:id="rId3"/>
+    <sheet name="Execution Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Scenarios" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,7 +421,7 @@
         <v>Target APK</v>
       </c>
       <c r="B3" t="str">
-        <v>AgroRent_OwnerPortal_Latest.apk (69.1 MB)</v>
+        <v>app-debug.apk (166.0 MB)</v>
       </c>
     </row>
     <row r="4">
@@ -435,31 +434,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Blocker Root Cause</v>
+        <v>Execution Mode</v>
       </c>
       <c r="B5" t="str">
-        <v>Zero configured AVD emulators found &amp; Appium CLI not installed globally</v>
+        <v>HOST AUDIT (BLOCKED)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Physical Device Policy</v>
+        <v>Target Device / AVD</v>
       </c>
       <c r="B6" t="str">
-        <v>Detached (Physical phone testing prohibited during local automated QA phase)</v>
+        <v>None</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Flutter Unit/Integration Tests</v>
+        <v>Flutter Unit/Widget Tests</v>
       </c>
       <c r="B7" t="str">
-        <v>30 files, 538 / 538 Passed (100% in mobile/test/)</v>
+        <v>30 files, 538 / 538 Passed (100%)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Planned Appium Scenarios</v>
+        <v>Appium Scenarios Total</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -467,22 +466,38 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>Appium Scenarios Passed</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Appium Scenarios Blocked</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Timestamp</v>
       </c>
-      <c r="B9" t="str">
-        <v>2026-10-27T06:11:54.998Z</v>
+      <c r="B11" t="str">
+        <v>2026-10-27T07:35:31.506Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -504,7 +519,10 @@
         <v>Status</v>
       </c>
       <c r="G1" t="str">
-        <v>RemediationRequirement</v>
+        <v>ExecutionType</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Evidence</v>
       </c>
     </row>
     <row r="2">
@@ -521,13 +539,16 @@
         <v>Verify APK cold launch, splash rendering, Riverpod initialization, and route redirection to /login</v>
       </c>
       <c r="E2" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F2" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G2" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="3">
@@ -544,13 +565,16 @@
         <v>Submit credentials for Farmer and Owner, verify JWT session storage, and check role-based dashboard landing</v>
       </c>
       <c r="E3" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F3" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G3" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="4">
@@ -567,13 +591,16 @@
         <v>Browse equipment listings, test category filters (TRACTOR, HARVESTER), apply search queries, and view equipment details</v>
       </c>
       <c r="E4" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F4" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G4" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="5">
@@ -590,13 +617,16 @@
         <v>Select rental duration, confirm pricing calculation, submit booking request, and verify state transition to PENDING</v>
       </c>
       <c r="E5" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F5" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G5" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +643,16 @@
         <v>Verify owner equipment listings, toggle equipment availability, and inspect maintenance schedules</v>
       </c>
       <c r="E6" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F6" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G6" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="7">
@@ -636,13 +669,16 @@
         <v>Review incoming booking requests, trigger Accept workflow, and verify booking status update to CONFIRMED</v>
       </c>
       <c r="E7" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F7" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G7" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="8">
@@ -659,13 +695,16 @@
         <v>Change language among English, Telugu, Hindi, Tamil, and Kannada; verify localized UI text across screens</v>
       </c>
       <c r="E8" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F8" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G8" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="9">
@@ -682,13 +721,16 @@
         <v>Test booking chat modal, verify sender/recipient display names, and check number masking privacy on calls</v>
       </c>
       <c r="E9" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F9" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G9" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="10">
@@ -705,13 +747,16 @@
         <v>Submit crop disease query to AI advisor, verify response parsing, and test graceful fallback when offline</v>
       </c>
       <c r="E10" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F10" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G10" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
     <row r="11">
@@ -728,106 +773,21 @@
         <v>Simulate network interruption, verify non-blocking snackbar alerts, and confirm no fatal app crashes occur</v>
       </c>
       <c r="E11" t="str">
-        <v>Android 14+ (UiAutomator2)</v>
+        <v>Android (UiAutomator2)</v>
       </c>
       <c r="F11" t="str">
-        <v>BLOCKED (MISSING_AVD)</v>
+        <v>BLOCKED</v>
       </c>
       <c r="G11" t="str">
-        <v>Requires local emulator setup</v>
+        <v>ENVIRONMENT_UNAVAILABLE</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Blocked by host machine lacking active Android AVD</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Component</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Path</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Android SDK</v>
-      </c>
-      <c r="B2" t="str">
-        <v>C:\Users\bhanu\AppData\Local\Android\Sdk</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DETECTED</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ADB Binary</v>
-      </c>
-      <c r="B3" t="str">
-        <v>platform-tools\adb.exe</v>
-      </c>
-      <c r="C3" t="str">
-        <v>OPERATIONAL</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Connected Devices</v>
-      </c>
-      <c r="B4" t="str">
-        <v>adb devices</v>
-      </c>
-      <c r="C4" t="str">
-        <v>0 ATTACHED</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Android Emulator</v>
-      </c>
-      <c r="B5" t="str">
-        <v>emulator.exe -list-avds</v>
-      </c>
-      <c r="C5" t="str">
-        <v>0 AVDs CONFIGURED (BLOCKER)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Appium 2.x CLI</v>
-      </c>
-      <c r="B6" t="str">
-        <v>appium --version</v>
-      </c>
-      <c r="C6" t="str">
-        <v>NOT INSTALLED IN PATH (BLOCKER)</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Flutter SDK</v>
-      </c>
-      <c r="B7" t="str">
-        <v>flutter.bat (3.47.5)</v>
-      </c>
-      <c r="C7" t="str">
-        <v>OPERATIONAL (538 Unit Tests Passed)</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>